--- a/fhir/core/ValueSet-dk-core-RegionalSubDivisionCodes.xlsx
+++ b/fhir/core/ValueSet-dk-core-RegionalSubDivisionCodes.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.5.0</t>
+    <t>3.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T17:27:08+01:00</t>
+    <t>2026-03-11T23:16:27+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,10 +99,22 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Codes</t>
-  </si>
-  <si>
-    <t>All codes</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>DK-84</t>
+  </si>
+  <si>
+    <t>DK-82</t>
+  </si>
+  <si>
+    <t>DK-81</t>
+  </si>
+  <si>
+    <t>DK-85</t>
+  </si>
+  <si>
+    <t>DK-83</t>
   </si>
   <si>
     <t/>
@@ -111,7 +123,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://hl7.dk/fhir/core/CodeSystem/dk-core-regional-subdivision-codes</t>
+    <t>urn:iso:std:iso:3166:-2</t>
   </si>
 </sst>
 </file>
@@ -375,7 +387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -386,26 +398,54 @@
       <c r="A1" t="s" s="1">
         <v>28</v>
       </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>32</v>
+      </c>
+      <c r="B5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/core/ValueSet-dk-core-RegionalSubDivisionCodes.xlsx
+++ b/fhir/core/ValueSet-dk-core-RegionalSubDivisionCodes.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.6.0</t>
+    <t>3.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T23:16:27+01:00</t>
+    <t>2026-05-30T15:25:27+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
